--- a/orders_raw.xlsx
+++ b/orders_raw.xlsx
@@ -7,76 +7,85 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="orders" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
-  <si>
-    <t>order_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust_ID </t>
-  </si>
-  <si>
-    <t>Order Amount</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
-    <t>order date</t>
-  </si>
-  <si>
-    <t>2024-03-01</t>
-  </si>
-  <si>
-    <t>2024-03-02</t>
-  </si>
-  <si>
-    <t>2024-03-03</t>
-  </si>
-  <si>
-    <t>2024-03-04</t>
-  </si>
-  <si>
-    <t>2024-03-05</t>
-  </si>
-  <si>
-    <t>2024-03-06</t>
-  </si>
-  <si>
-    <t>2024-03-07</t>
-  </si>
-  <si>
-    <t>2024-03-08</t>
-  </si>
-  <si>
-    <t>2024-04-01</t>
-  </si>
-  <si>
-    <t>2024-04-02</t>
-  </si>
-  <si>
-    <t>2024-04-03</t>
-  </si>
-  <si>
-    <t>2024-04-04</t>
-  </si>
-  <si>
-    <t>2024-04-05</t>
-  </si>
-  <si>
-    <t>2024-04-06</t>
-  </si>
-  <si>
-    <t>2024-04-07</t>
-  </si>
-  <si>
-    <t>2024-04-08</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+  <si>
+    <t>Order_Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust_Id </t>
+  </si>
+  <si>
+    <t>Product_Id</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Order Date</t>
+  </si>
+  <si>
+    <t>P01</t>
+  </si>
+  <si>
+    <t>P02</t>
+  </si>
+  <si>
+    <t>P03</t>
+  </si>
+  <si>
+    <t>P04</t>
+  </si>
+  <si>
+    <t>P05</t>
+  </si>
+  <si>
+    <t>P06</t>
+  </si>
+  <si>
+    <t>P07</t>
+  </si>
+  <si>
+    <t>P08</t>
+  </si>
+  <si>
+    <t>P99</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>2024-05-02</t>
+  </si>
+  <si>
+    <t>2024-05-03</t>
+  </si>
+  <si>
+    <t>2024-05-04</t>
+  </si>
+  <si>
+    <t>2024-05-05</t>
+  </si>
+  <si>
+    <t>2024-06-01</t>
+  </si>
+  <si>
+    <t>2024-06-02</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>2024-06-04</t>
+  </si>
+  <si>
+    <t>2024-06-05</t>
   </si>
 </sst>
 </file>
@@ -433,16 +442,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>201</v>
-      </c>
-      <c r="C2">
-        <v>1200</v>
+        <v>301</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -450,16 +459,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>202</v>
-      </c>
-      <c r="C3">
-        <v>850</v>
+        <v>302</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -467,16 +476,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>203</v>
-      </c>
-      <c r="C4">
-        <v>2100</v>
+        <v>303</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -484,16 +493,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>205</v>
-      </c>
-      <c r="C5">
-        <v>430</v>
+        <v>304</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -501,16 +510,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>207</v>
-      </c>
-      <c r="C6">
-        <v>3200</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
+        <v>305</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -518,16 +524,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>208</v>
-      </c>
-      <c r="C7">
-        <v>990</v>
+        <v>306</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -535,13 +541,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>209</v>
+        <v>307</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -549,16 +558,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>210</v>
-      </c>
-      <c r="C9">
-        <v>1750</v>
+        <v>308</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -566,16 +575,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>201</v>
-      </c>
-      <c r="C10">
-        <v>620</v>
+        <v>309</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -583,16 +592,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>202</v>
-      </c>
-      <c r="C11">
-        <v>1430</v>
+        <v>310</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -600,16 +609,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>205</v>
-      </c>
-      <c r="C12">
-        <v>2900</v>
+        <v>301</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -617,16 +626,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>208</v>
-      </c>
-      <c r="C13">
-        <v>780</v>
+        <v>303</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -634,16 +643,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>209</v>
-      </c>
-      <c r="C14">
-        <v>1100</v>
+        <v>305</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -651,16 +660,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>999</v>
-      </c>
-      <c r="C15">
-        <v>540</v>
+        <v>307</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -668,16 +677,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>203</v>
-      </c>
-      <c r="C16">
-        <v>3300</v>
-      </c>
-      <c r="D16">
-        <v>20</v>
+        <v>309</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -685,13 +691,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>207</v>
+        <v>401</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -699,16 +708,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>210</v>
-      </c>
-      <c r="C18">
-        <v>990</v>
+        <v>302</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -716,16 +725,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>201</v>
-      </c>
-      <c r="C19">
-        <v>1580</v>
+        <v>304</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -733,16 +742,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>205</v>
-      </c>
-      <c r="C20">
-        <v>720</v>
+        <v>306</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -750,16 +759,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>998</v>
-      </c>
-      <c r="C21">
-        <v>2200</v>
+        <v>402</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
